--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487610_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487610_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2367</v>
+        <v>3.546</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3853</v>
+        <v>3.5855</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1486</v>
+        <v>-0.0396</v>
       </c>
       <c r="G2" t="n">
         <v>4.0916</v>
@@ -610,13 +610,13 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0668</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0863</v>
+        <v>0.2865</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1532</v>
+        <v>-1.0442</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5642</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9782</v>
+        <v>1.9625</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8937</v>
+        <v>1.7145</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.248</v>
       </c>
       <c r="G3" t="n">
         <v>0.401</v>
@@ -688,13 +688,13 @@
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0249</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8748</v>
+        <v>0.6956</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8499</v>
+        <v>-0.6864</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1616</v>
+        <v>0.6883</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4738</v>
+        <v>1.9733</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3122</v>
+        <v>-1.285</v>
       </c>
       <c r="G4" t="n">
         <v>-1.3159</v>
@@ -766,13 +766,13 @@
         <v>2.1344</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2133</v>
+        <v>-0.2599</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3656</v>
+        <v>-0.1349</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1523</v>
+        <v>-0.125</v>
       </c>
       <c r="V4" t="n">
         <v>2.0701</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0206</v>
+        <v>-0.3431</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7323</v>
+        <v>-0.9325</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7529</v>
+        <v>0.5894</v>
       </c>
       <c r="G5" t="n">
         <v>0.0208</v>
@@ -844,13 +844,13 @@
         <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1938</v>
+        <v>-0.1699</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5103</v>
+        <v>0.3101</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3165</v>
+        <v>-0.48</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. PUNZANO VIEDMA</t>
+          <t>L. SCHIEBELHUT LUIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4753</v>
+        <v>-1.1372</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9727</v>
+        <v>0.1285</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5026</v>
+        <v>-1.2658</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2675</v>
+        <v>1.9933</v>
       </c>
       <c r="H6" t="n">
-        <v>0.519</v>
+        <v>0.5841</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7485000000000001</v>
+        <v>1.4092</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6204</v>
+        <v>4.3653</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9886</v>
+        <v>1.8661</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6318</v>
+        <v>2.4992</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3529</v>
+        <v>-2.372</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4696</v>
+        <v>-1.282</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1168</v>
+        <v>-1.09</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5821</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9403</v>
+        <v>-3.8806</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3582</v>
+        <v>2.7164</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6548</v>
+        <v>-0.7425</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6528</v>
+        <v>-0.3561</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.002</v>
+        <v>-0.3864</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.506</v>
+        <v>-1.2239</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.506</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. SCHIEBELHUT LUIS</t>
+          <t>T. PUNZANO VIEDMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5531</v>
+        <v>-1.1629</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5326</v>
+        <v>-0.5513</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0205</v>
+        <v>-0.6116</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9933</v>
+        <v>1.2675</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5841</v>
+        <v>0.519</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4092</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3653</v>
+        <v>1.6204</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8661</v>
+        <v>0.9886</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4992</v>
+        <v>0.6318</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.372</v>
+        <v>-0.3529</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.282</v>
+        <v>-0.4696</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.09</v>
+        <v>0.1168</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1642</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.8806</v>
+        <v>-1.9403</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7164</v>
+        <v>1.3582</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1584</v>
+        <v>-0.3424</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0173</v>
+        <v>-0.2314</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1411</v>
+        <v>-0.111</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2239</v>
+        <v>-1.506</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2239</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6143</v>
+        <v>-1.3868</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0167</v>
+        <v>-1.8165</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4024</v>
+        <v>0.4297</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0925</v>
@@ -1078,13 +1078,13 @@
         <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3576</v>
+        <v>-0.1301</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0258</v>
+        <v>0.226</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3833</v>
+        <v>-0.3561</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>M. ESTAPE ROIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4788</v>
+        <v>-2.6517</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4246</v>
+        <v>-3.4456</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0542</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6223</v>
+        <v>-3.6709</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5612</v>
+        <v>-1.8669</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0611</v>
+        <v>-1.804</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7531</v>
+        <v>-2.2009</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9155</v>
+        <v>-0.9474</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1624</v>
+        <v>-1.2535</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8692</v>
+        <v>-1.47</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3542</v>
+        <v>-0.9195</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2235</v>
+        <v>-0.5506</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
         <v>2.3284</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8151</v>
+        <v>-0.339</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9867</v>
+        <v>-0.2745</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1716</v>
+        <v>-0.0645</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.0597</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.3418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ESTAPE ROIZ</t>
+          <t>D. SHIELDS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.24</v>
+        <v>-2.7854</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0066</v>
+        <v>-2.7174</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7665999999999999</v>
+        <v>-0.068</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.6709</v>
+        <v>-2.1153</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8669</v>
+        <v>-2.5507</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.804</v>
+        <v>0.4354</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2009</v>
+        <v>-1.7966</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9474</v>
+        <v>-1.8372</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2535</v>
+        <v>0.0406</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.47</v>
+        <v>-0.3187</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9195</v>
+        <v>-0.7135</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5506</v>
+        <v>0.3948</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3284</v>
+        <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9273</v>
+        <v>-0.8642</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8356</v>
+        <v>0.0493</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0917</v>
+        <v>-0.9135</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. SHIELDS</t>
+          <t>T. VERDERA BENASSAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3826</v>
+        <v>-3.3772</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1784</v>
+        <v>-3.6738</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2042</v>
+        <v>0.2967</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1153</v>
+        <v>-3.26</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5507</v>
+        <v>-2.9297</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4354</v>
+        <v>-0.3303</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7966</v>
+        <v>-3.8816</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8372</v>
+        <v>-3.2955</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0406</v>
+        <v>-0.5861</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3187</v>
+        <v>0.6216</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7135</v>
+        <v>0.3658</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3948</v>
+        <v>0.2558</v>
       </c>
       <c r="P11" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4614</v>
+        <v>-0.1455</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4116</v>
+        <v>-0.0743</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0498</v>
+        <v>-0.0712</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.9418</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. VERDERA BENASSAR</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1112</v>
+        <v>-5.0536</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4351</v>
+        <v>-2.7269</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3239</v>
+        <v>-2.3267</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.26</v>
+        <v>-2.6223</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.9297</v>
+        <v>-1.5612</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3303</v>
+        <v>-1.0611</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.8816</v>
+        <v>-1.7531</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.2955</v>
+        <v>-1.9155</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5861</v>
+        <v>0.1624</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6216</v>
+        <v>-0.8692</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3658</v>
+        <v>0.3542</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2558</v>
+        <v>-1.2235</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9702</v>
+        <v>0.3881</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9702</v>
+        <v>2.3284</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8794999999999999</v>
+        <v>0.2403</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8356</v>
+        <v>0.6844</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0439</v>
+        <v>-0.4441</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9418</v>
+        <v>-3.0597</v>
       </c>
       <c r="W12" t="n">
         <v>0.2821</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2239</v>
+        <v>-3.3418</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.6698</v>
+        <v>-6.8213</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.2734</v>
+        <v>-6.7518</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3965</v>
+        <v>-0.0694</v>
       </c>
       <c r="G13" t="n">
         <v>-8.157400000000001</v>
@@ -1468,13 +1468,13 @@
         <v>1.5523</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6483</v>
+        <v>-0.7997</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8951</v>
+        <v>-0.3735</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7532</v>
+        <v>-0.4262</v>
       </c>
       <c r="V13" t="n">
         <v>1.5537</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.128</v>
+        <v>-18.5224</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.8196</v>
+        <v>-15.214</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.3085</v>
+        <v>-3.3084</v>
       </c>
       <c r="G14" t="n">
         <v>-13.4601</v>
@@ -1519,16 +1519,16 @@
         <v>-4.0595</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.592699999999999</v>
+        <v>-3.5927</v>
       </c>
       <c r="K14" t="n">
         <v>-3.7319</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1394000000000002</v>
+        <v>0.1393999999999997</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.867499999999998</v>
+        <v>-9.8675</v>
       </c>
       <c r="N14" t="n">
         <v>-5.6685</v>
@@ -1537,7 +1537,7 @@
         <v>-4.1988</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9105</v>
+        <v>2.910500000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-17.4629</v>
@@ -1546,28 +1546,28 @@
         <v>20.3734</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.907</v>
+        <v>-4.3012</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2014999999999996</v>
+        <v>0.8071999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.108499999999999</v>
+        <v>-5.108599999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.671799999999999</v>
+        <v>-3.6718</v>
       </c>
       <c r="W14" t="n">
         <v>5.0344</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.706</v>
+        <v>-8.706000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. GARCIA-LARRACHE SEGURA</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6831</v>
+        <v>3.5202</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0133</v>
+        <v>0.2402</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6698</v>
+        <v>3.28</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3188</v>
+        <v>2.5171</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1114</v>
+        <v>1.7458</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4302</v>
+        <v>0.7713</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7442</v>
+        <v>1.1118</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8362000000000001</v>
+        <v>0.4573</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5804</v>
+        <v>0.6546</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4254</v>
+        <v>1.4053</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2752</v>
+        <v>1.2885</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1502</v>
+        <v>0.1168</v>
       </c>
       <c r="P15" t="n">
         <v>-0.194</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1344</v>
+        <v>-1.9403</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5583</v>
+        <v>-0.261</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4035</v>
+        <v>-0.3895</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1548</v>
+        <v>0.1285</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.4582</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.4582</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. HERMOSO ALCUBILLA</t>
+          <t>J. GARCIA-LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5048</v>
+        <v>3.1131</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6197</v>
+        <v>0.9123</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8851</v>
+        <v>2.2008</v>
       </c>
       <c r="G16" t="n">
-        <v>4.7631</v>
+        <v>1.3188</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8489</v>
+        <v>-1.1114</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9142</v>
+        <v>2.4302</v>
       </c>
       <c r="J16" t="n">
-        <v>5.1769</v>
+        <v>1.7442</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5787</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5982</v>
+        <v>2.5804</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4138</v>
+        <v>-0.4254</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2702</v>
+        <v>-0.2752</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.1502</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.5224</v>
+        <v>-0.194</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.0747</v>
+        <v>-2.1344</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5523</v>
+        <v>1.9403</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5462</v>
+        <v>1.9883</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5175</v>
+        <v>1.3024</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0287</v>
+        <v>0.6859</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>E. MARTINEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.157</v>
+        <v>2.9116</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3403</v>
+        <v>1.6347</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8167</v>
+        <v>1.2768</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5171</v>
+        <v>3.6114</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7458</v>
+        <v>1.4475</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7713</v>
+        <v>2.1638</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1118</v>
+        <v>2.6125</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4573</v>
+        <v>0.7044</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6546</v>
+        <v>1.908</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4053</v>
+        <v>0.9989</v>
       </c>
       <c r="N17" t="n">
-        <v>1.2885</v>
+        <v>0.7431</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1168</v>
+        <v>0.2558</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9403</v>
+        <v>-1.1642</v>
       </c>
       <c r="R17" t="n">
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6243</v>
+        <v>0.224</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2894</v>
+        <v>0.1864</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3349</v>
+        <v>0.0376</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4582</v>
+        <v>-1.506</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4582</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. MARTINEZ ALVAREZ</t>
+          <t>M. HERMOSO ALCUBILLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7786</v>
+        <v>2.8191</v>
       </c>
       <c r="E18" t="n">
-        <v>1.935</v>
+        <v>1.7188</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8436</v>
+        <v>1.1003</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6114</v>
+        <v>4.7631</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4475</v>
+        <v>2.8489</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1638</v>
+        <v>1.9142</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6125</v>
+        <v>5.1769</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7044</v>
+        <v>2.5787</v>
       </c>
       <c r="L18" t="n">
-        <v>1.908</v>
+        <v>2.5982</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9989</v>
+        <v>-0.4138</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7431</v>
+        <v>0.2702</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2558</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5821</v>
+        <v>-2.5224</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1642</v>
+        <v>-4.0747</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7463</v>
+        <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0911</v>
+        <v>0.8605</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4867</v>
+        <v>0.6166</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3957</v>
+        <v>0.244</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.506</v>
+        <v>-0.2821</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.506</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. FUENTE DIEZ</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.7242</v>
+        <v>2.5704</v>
       </c>
       <c r="E19" t="n">
-        <v>3.4138</v>
+        <v>0.4307</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6896</v>
+        <v>2.1397</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5593</v>
+        <v>2.0578</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1822</v>
+        <v>2.3826</v>
       </c>
       <c r="I19" t="n">
-        <v>0.377</v>
+        <v>-0.3248</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6062</v>
+        <v>1.5147</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9567</v>
+        <v>2.1009</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6495</v>
+        <v>-0.5861</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0469</v>
+        <v>0.5431</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7744</v>
+        <v>0.2817</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2725</v>
+        <v>0.2614</v>
       </c>
       <c r="P19" t="n">
         <v>-0.3881</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5821</v>
+        <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9888</v>
+        <v>0.9006</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2135</v>
+        <v>0.8563</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2248</v>
+        <v>0.0443</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>P. FUENTE DIEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3241</v>
+        <v>2.2053</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1699</v>
+        <v>2.8132</v>
       </c>
       <c r="F20" t="n">
-        <v>1.494</v>
+        <v>-0.6078</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0578</v>
+        <v>1.5593</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3826</v>
+        <v>1.1822</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3248</v>
+        <v>0.377</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5147</v>
+        <v>2.6062</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1009</v>
+        <v>1.9567</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5861</v>
+        <v>0.6495</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5431</v>
+        <v>-1.0469</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2817</v>
+        <v>-0.7744</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2614</v>
+        <v>-0.2725</v>
       </c>
       <c r="P20" t="n">
         <v>-0.3881</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5523</v>
+        <v>0.5821</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3457</v>
+        <v>0.4699</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2557</v>
+        <v>0.6129</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6014</v>
+        <v>-0.143</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. LAPASTORA ARACIL</t>
+          <t>L. GARCIA LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2644</v>
+        <v>2.1079</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7689</v>
+        <v>2.2833</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0333</v>
+        <v>-0.1754</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2283</v>
+        <v>1.157</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.002</v>
+        <v>1.7548</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2263</v>
+        <v>-0.5978</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.6878</v>
+        <v>1.8493</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.6116</v>
+        <v>1.7631</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0762</v>
+        <v>0.0862</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4595</v>
+        <v>-0.6923</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6096</v>
+        <v>-0.0083</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1502</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7761</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5987</v>
+        <v>0.9032</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1592</v>
+        <v>1.1504</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4395</v>
+        <v>-0.2473</v>
       </c>
       <c r="V21" t="n">
-        <v>2.1179</v>
+        <v>0.0478</v>
       </c>
       <c r="W21" t="n">
-        <v>2.7298</v>
+        <v>1.2239</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6119</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.1128</v>
+        <v>1.9991</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6274</v>
+        <v>-0.6264</v>
       </c>
       <c r="F22" t="n">
-        <v>2.7402</v>
+        <v>2.6255</v>
       </c>
       <c r="G22" t="n">
         <v>1.4881</v>
@@ -2170,13 +2170,13 @@
         <v>2.1344</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2649</v>
+        <v>1.1513</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.387</v>
+        <v>0.614</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6519</v>
+        <v>0.5373</v>
       </c>
       <c r="V22" t="n">
         <v>0.3299</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. GARCIA LARRACHE SEGURA</t>
+          <t>J. LAPASTORA ARACIL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9796</v>
+        <v>1.4929</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5826</v>
+        <v>-0.3685</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.603</v>
+        <v>1.8613</v>
       </c>
       <c r="G23" t="n">
-        <v>1.157</v>
+        <v>-2.2283</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7548</v>
+        <v>-2.002</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5978</v>
+        <v>-0.2263</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8493</v>
+        <v>-2.6878</v>
       </c>
       <c r="K23" t="n">
-        <v>1.7631</v>
+        <v>-2.6116</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0862</v>
+        <v>-0.0762</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6923</v>
+        <v>0.4595</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0083</v>
+        <v>0.6096</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.1502</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.7761</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2252</v>
+        <v>0.8272</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4497</v>
+        <v>0.5596</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.2675</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0478</v>
+        <v>2.1179</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2239</v>
+        <v>2.7298</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1761</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. ALONSO GONZÁLEZ</t>
+          <t>N. LASUNCION MARIBLANCA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.3978</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0606</v>
+        <v>-3.6272</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1335</v>
+        <v>4.025</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1335</v>
+        <v>-1.0586</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2.208</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1335</v>
+        <v>-3.2666</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-3.1483</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.7744</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-3.9228</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1335</v>
+        <v>2.0897</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.4335</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1335</v>
+        <v>0.6562</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.5523</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0606</v>
+        <v>-0.0793</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0606</v>
+        <v>-0.4624</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>0.3831</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2.1179</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.1179</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>N. LASUNCION MARIBLANCA</t>
+          <t>M. ALONSO GONZÁLEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2568</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.9275</v>
+        <v>-0.0606</v>
       </c>
       <c r="F25" t="n">
-        <v>3.6707</v>
+        <v>0.1335</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.0586</v>
+        <v>0.1335</v>
       </c>
       <c r="H25" t="n">
-        <v>2.208</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.2666</v>
+        <v>0.1335</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.1483</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7744</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.9228</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.0897</v>
+        <v>0.1335</v>
       </c>
       <c r="N25" t="n">
-        <v>1.4335</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6562</v>
+        <v>0.1335</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.5821</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.1344</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5523</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.734</v>
+        <v>-0.0606</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7627</v>
+        <v>-0.0606</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0287</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>2.1179</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.1179</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.2166</v>
+        <v>-2.0803</v>
       </c>
       <c r="E26" t="n">
         <v>-2.0422</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1744</v>
+        <v>-0.0381</v>
       </c>
       <c r="G26" t="n">
         <v>-1.8592</v>
@@ -2482,13 +2482,13 @@
         <v>0.9702</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1514</v>
+        <v>-0.0151</v>
       </c>
       <c r="T26" t="n">
         <v>0.1222</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2736</v>
+        <v>-0.1374</v>
       </c>
       <c r="V26" t="n">
         <v>-1.1761</v>
@@ -2515,25 +2515,25 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>19.1281</v>
+        <v>21.13</v>
       </c>
       <c r="E27" t="n">
-        <v>3.308199999999999</v>
+        <v>3.308300000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>15.8199</v>
+        <v>17.8216</v>
       </c>
       <c r="G27" t="n">
         <v>13.46</v>
       </c>
       <c r="H27" t="n">
-        <v>9.400199999999998</v>
+        <v>9.400200000000002</v>
       </c>
       <c r="I27" t="n">
         <v>4.059600000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>9.867199999999997</v>
+        <v>9.8672</v>
       </c>
       <c r="K27" t="n">
         <v>5.6684</v>
@@ -2548,7 +2548,7 @@
         <v>3.7318</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.139</v>
+        <v>-0.1390000000000001</v>
       </c>
       <c r="P27" t="n">
         <v>-2.9105</v>
@@ -2560,13 +2560,13 @@
         <v>17.4631</v>
       </c>
       <c r="S27" t="n">
-        <v>4.9068</v>
+        <v>6.909</v>
       </c>
       <c r="T27" t="n">
         <v>5.108300000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2016999999999999</v>
+        <v>1.8005</v>
       </c>
       <c r="V27" t="n">
         <v>3.6717</v>
